--- a/Sheets/decor_catalog.xlsx
+++ b/Sheets/decor_catalog.xlsx
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9847ce9c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=776acf03")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=0edd4353")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=3f31692b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=914f1301")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=b0bfafac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2033641c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -2021,20 +2021,20 @@
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky-koi-betta</t>
+          <t xml:space="preserve">royal-koi-betta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=2ce9ca1f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh da trời, đỏ, cam · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Koi xanh hoàng gia, đỏ, vàng · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E9" s="4">
@@ -2054,15 +2054,15 @@
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky-koi-betta-m4</t>
+          <t xml:space="preserve">sky-koi-betta</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=abac46f1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta M4</t>
+          <t xml:space="preserve">Sky Koi Betta</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2079,6 +2079,39 @@
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sky-koi-betta-m4</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta M4</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xanh da trời, đỏ, cam · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1.5</t>
         </is>
@@ -2234,7 +2267,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9847ce9c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2312,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=776acf03")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -2324,7 +2357,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=0edd4353")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2402,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=3f31692b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -2406,7 +2439,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=914f1301")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -2443,7 +2476,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=b0bfafac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -2480,7 +2513,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2033641c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -2521,15 +2554,15 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">RoyalKoiBetta</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=2ce9ca1f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -2566,43 +2599,88 @@
     <row r="12" ht="66" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">SkyKoiBetta</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
-      <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=abac46f1")</f>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MeshyColour</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2774,7 +2852,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9847ce9c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2897,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=776acf03")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -2864,7 +2942,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=0edd4353")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -2909,7 +2987,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=3f31692b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -2954,7 +3032,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=914f1301")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -2999,7 +3077,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=b0bfafac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -3044,7 +3122,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2033641c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -3085,15 +3163,15 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">RoyalKoiBetta</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=2ce9ca1f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3130,43 +3208,88 @@
     <row r="12" ht="66" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">SkyKoiBetta</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
-      <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=abac46f1")</f>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3195,6 +3318,7 @@
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3275,6 +3399,11 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">envReflection</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">baseTexture</t>
         </is>
       </c>
@@ -3332,6 +3461,9 @@
         <v>1</v>
       </c>
       <c r="P2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3">
         <v>0</v>
       </c>
     </row>
@@ -3382,12 +3514,15 @@
         <v>0.35</v>
       </c>
       <c r="N3" s="4">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O3" s="4">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
         <v>1</v>
       </c>
     </row>
@@ -3398,7 +3533,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9847ce9c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -3466,6 +3601,11 @@
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3478,7 +3618,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=776acf03")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -3546,6 +3686,11 @@
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3558,7 +3703,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=0edd4353")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -3575,10 +3720,8 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="F6" s="4">
+        <v>0</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -3626,6 +3769,11 @@
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3638,7 +3786,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=3f31692b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -3694,6 +3842,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -3702,7 +3855,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=914f1301")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -3758,6 +3911,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -3766,7 +3924,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=b0bfafac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -3814,6 +3972,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -3822,7 +3985,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2033641c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -3890,6 +4053,11 @@
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3898,15 +4066,15 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">RoyalKoiBetta</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=2ce9ca1f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3970,6 +4138,11 @@
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3978,78 +4151,168 @@
     <row r="12" ht="66" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">SkyKoiBetta</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
-      <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=abac46f1")</f>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4241,7 +4504,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9847ce9c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -4301,7 +4564,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=776acf03")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -4361,7 +4624,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=0edd4353")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -4421,7 +4684,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=3f31692b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -4471,7 +4734,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=914f1301")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -4521,7 +4784,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=b0bfafac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -4567,7 +4830,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2033641c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -4623,15 +4886,15 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">RoyalKoiBetta</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=2ce9ca1f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4683,58 +4946,118 @@
     <row r="12" ht="66" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">SkyKoiBetta</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
-      <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=abac46f1")</f>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/Sheets/decor_catalog.xlsx
+++ b/Sheets/decor_catalog.xlsx
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>0.35</v>
       </c>
       <c r="N3" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="O3" s="4">
         <v>1.2</v>
-      </c>
-      <c r="O3" s="4">
-        <v>1.4</v>
       </c>
       <c r="P3" s="4">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=1750119c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=24cdd56d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=909866ea")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=24a08da3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=51f5b300")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=7ab9c805")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=de42c597")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=d558dee5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=4b2789cf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=d0d3fecf")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>

--- a/Sheets/decor_catalog.xlsx
+++ b/Sheets/decor_catalog.xlsx
@@ -1790,20 +1790,20 @@
     <row r="2" ht="66" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue-flame-betta</t>
+          <t xml:space="preserve">black-samurai-betta</t>
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Samurai Đen</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh dương, đỏ, cam · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Samurai đen, vảy trắng bạc · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E2" s="4">
@@ -1823,20 +1823,20 @@
     <row r="3" ht="66" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">galaxy-betta</t>
+          <t xml:space="preserve">blue-bee-betta</t>
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galaxy Betta</t>
+          <t xml:space="preserve">Betta Ong Xanh</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh ngọc, xanh dương, đen · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Đen xanh dương, khoang vàng · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E3" s="4">
@@ -1856,20 +1856,20 @@
     <row r="4" ht="66" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">koi-betta</t>
+          <t xml:space="preserve">blue-flame-betta</t>
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Betta</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi xanh, đỏ, vàng, tím · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Xanh dương, đỏ, cam · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E4" s="4">
@@ -1889,20 +1889,20 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">koi-nemo</t>
+          <t xml:space="preserve">blue-panda-betta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Nemo Betta</t>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh dương, trắng, đen · Koi Nemo đuôi tròn</t>
+          <t xml:space="preserve">Thân trắng hồng đốm đen, đuôi trắng mảng xanh dương đậm · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E5" s="4">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Butterfly</t>
+          <t xml:space="preserve">Solid</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1922,20 +1922,20 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">plakat</t>
+          <t xml:space="preserve">blue-wild-betta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Koi</t>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đỏ, cam, xanh · Plakat đuôi ngắn</t>
+          <t xml:space="preserve">Betta hoang dã xanh lam, đốm đen trên vây · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E6" s="4">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi</t>
+          <t xml:space="preserve">Solid</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1955,20 +1955,20 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">plakat-galaxy</t>
+          <t xml:space="preserve">colorful-betta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
+          <t xml:space="preserve">Colorful Betta</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Galaxy: thân trắng ngọc mảng đỏ tươi, lưng vảy đen, mang trắng viền đỏ, vây vàng nghệ</t>
+          <t xml:space="preserve">Xanh dương, đỏ, trắng, vàng · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E7" s="4">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiGalaxy</t>
+          <t xml:space="preserve">Solid</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1988,20 +1988,20 @@
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">red-steel-betta</t>
+          <t xml:space="preserve">galaxy-betta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Galaxy Betta</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thân xanh thép, vây đỏ trắng · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Xanh ngọc, xanh dương, đen · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E8" s="4">
@@ -2021,20 +2021,20 @@
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">royal-koi-betta</t>
+          <t xml:space="preserve">gold-tiger-betta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Betta Hổ Vàng</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi xanh hoàng gia, đỏ, vàng · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Thân cam vàng đốm đen, đầu trắng hồng, đuôi đen ánh tím · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E9" s="4">
@@ -2054,20 +2054,20 @@
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky-koi-betta</t>
+          <t xml:space="preserve">koi-betta</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Koi Betta</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh da trời, đỏ, cam · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Koi xanh, đỏ, vàng, tím · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E10" s="4">
@@ -2087,20 +2087,20 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky-koi-betta-m4</t>
+          <t xml:space="preserve">koi-nemo</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta M4</t>
+          <t xml:space="preserve">Koi Nemo Betta</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh da trời, đỏ, cam · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Xanh dương, trắng, đen · Koi Nemo đuôi tròn</t>
         </is>
       </c>
       <c r="E11" s="4">
@@ -2108,10 +2108,307 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Butterfly</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nemo-koi-betta</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nemo Koi Betta</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi đỏ, cam, xanh dương, trắng · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Solid</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plakat</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Koi</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đỏ, cam, xanh · Plakat đuôi ngắn</t>
+        </is>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plakat-galaxy</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Galaxy</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi Galaxy: thân trắng ngọc mảng đỏ tươi, lưng vảy đen, mang trắng viền đỏ, vây vàng nghệ</t>
+        </is>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KoiGalaxy</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">purple-ruby-betta</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thân tím hồng, đầu và vây đỏ hồng ngọc viền trắng · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red-steel-betta</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Steel Betta</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thân xanh thép, vây đỏ trắng · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">royal-koi-betta</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Royal Koi</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi xanh hoàng gia, đỏ, vàng · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sky-koi-betta</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xanh da trời, đỏ, cam · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sky-koi-betta-m4</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta M4</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xanh da trời, đỏ, cam · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teal-white-betta</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thân trắng, đuôi xanh ngọc lam, vây bụng cam · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1.5</t>
         </is>
@@ -2263,15 +2560,15 @@
     <row r="4" ht="66" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueFlameBetta</t>
+          <t xml:space="preserve">BlackSamuraiBetta</t>
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Samurai Đen</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -2308,15 +2605,15 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GalaxyBetta</t>
+          <t xml:space="preserve">BlueBeeBetta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galaxy Betta</t>
+          <t xml:space="preserve">Betta Ong Xanh</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2353,15 +2650,15 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiBetta</t>
+          <t xml:space="preserve">BlueFlameBetta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Betta</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2398,126 +2695,150 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiNemoRig</t>
+          <t xml:space="preserve">BluePandaBetta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Nemo Betta</t>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E7" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="F7" s="4">
-        <v>3</v>
-      </c>
-      <c r="G7" s="4">
-        <v>8</v>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Butterfly</t>
-        </is>
-      </c>
-      <c r="I7" s="4">
-        <v>3</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat</t>
+          <t xml:space="preserve">BlueWildBetta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Koi</t>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E8" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="F8" s="4">
-        <v>3</v>
-      </c>
-      <c r="G8" s="4">
-        <v>8</v>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi</t>
-        </is>
-      </c>
-      <c r="I8" s="4">
-        <v>3</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PlakatGalaxy</t>
+          <t xml:space="preserve">ColorfulBetta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
+          <t xml:space="preserve">Colorful Betta</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E9" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="F9" s="4">
-        <v>3</v>
-      </c>
-      <c r="G9" s="4">
-        <v>8</v>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiGalaxy</t>
-        </is>
-      </c>
-      <c r="I9" s="4">
-        <v>3</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedSteelBetta</t>
+          <t xml:space="preserve">GalaxyBetta</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Galaxy Betta</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2554,15 +2875,15 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RoyalKoiBetta</t>
+          <t xml:space="preserve">GoldTigerBetta</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Betta Hổ Vàng</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -2599,15 +2920,15 @@
     <row r="12" ht="66" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">KoiBetta</t>
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Koi Betta</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2644,43 +2965,424 @@
     <row r="13" ht="66" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">KoiNemoRig</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi Nemo Betta</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4">
+        <v>8</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Butterfly</t>
+        </is>
+      </c>
+      <c r="I13" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NemoKoiBetta</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nemo Koi Betta</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Koi</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>8</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi</t>
+        </is>
+      </c>
+      <c r="I15" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PlakatGalaxy</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Galaxy</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>8</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KoiGalaxy</t>
+        </is>
+      </c>
+      <c r="I16" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PurpleRubyBetta</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedSteelBetta</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Steel Betta</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoyalKoiBetta</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Royal Koi</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkyKoiBetta</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
-      <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B21" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MeshyColour</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TealWhiteBetta</t>
+        </is>
+      </c>
+      <c r="B22" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2848,15 +3550,15 @@
     <row r="4" ht="66" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueFlameBetta</t>
+          <t xml:space="preserve">BlackSamuraiBetta</t>
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Samurai Đen</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -2893,15 +3595,15 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GalaxyBetta</t>
+          <t xml:space="preserve">BlueBeeBetta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galaxy Betta</t>
+          <t xml:space="preserve">Betta Ong Xanh</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2938,15 +3640,15 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiBetta</t>
+          <t xml:space="preserve">BlueFlameBetta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Betta</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2983,35 +3685,35 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiNemoRig</t>
+          <t xml:space="preserve">BluePandaBetta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Nemo Betta</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#1F4FD1</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#FFFFFF</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#171717</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#FFD133</t>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -3028,35 +3730,35 @@
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat</t>
+          <t xml:space="preserve">BlueWildBetta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Koi</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#FFD133</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#171717</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#FFFFFF</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#FFD133</t>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -3073,60 +3775,60 @@
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PlakatGalaxy</t>
+          <t xml:space="preserve">ColorfulBetta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#E0E0E0</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#38393D</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#FF0808</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#FFA80A</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#9E6B38</t>
-        </is>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#4C4C54</t>
+          <t xml:space="preserve">Colorful Betta</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedSteelBetta</t>
+          <t xml:space="preserve">GalaxyBetta</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Galaxy Betta</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -3163,15 +3865,15 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RoyalKoiBetta</t>
+          <t xml:space="preserve">GoldTigerBetta</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Betta Hổ Vàng</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3208,15 +3910,15 @@
     <row r="12" ht="66" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">KoiBetta</t>
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Koi Betta</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -3253,43 +3955,448 @@
     <row r="13" ht="66" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">KoiNemoRig</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi Nemo Betta</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#1F4FD1</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#FFFFFF</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#171717</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#FFD133</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NemoKoiBetta</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nemo Koi Betta</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Koi</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#FFD133</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#171717</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#FFFFFF</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#FFD133</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PlakatGalaxy</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Galaxy</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#E0E0E0</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#38393D</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#FF0808</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#FFA80A</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#9E6B38</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#4C4C54</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PurpleRubyBetta</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedSteelBetta</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Steel Betta</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoyalKoiBetta</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Royal Koi</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkyKoiBetta</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
-      <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B21" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TealWhiteBetta</t>
+        </is>
+      </c>
+      <c r="B22" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3514,7 +4621,7 @@
         <v>0.35</v>
       </c>
       <c r="N3" s="4">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="O3" s="4">
         <v>1.2</v>
@@ -3529,15 +4636,15 @@
     <row r="4" ht="66" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueFlameBetta</t>
+          <t xml:space="preserve">BlackSamuraiBetta</t>
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Samurai Đen</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -3614,15 +4721,15 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GalaxyBetta</t>
+          <t xml:space="preserve">BlueBeeBetta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galaxy Betta</t>
+          <t xml:space="preserve">Betta Ong Xanh</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3699,15 +4806,15 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiBetta</t>
+          <t xml:space="preserve">BlueFlameBetta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Betta</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3720,8 +4827,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="F6" s="4">
-        <v>0</v>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -3782,40 +4891,56 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiNemoRig</t>
+          <t xml:space="preserve">BluePandaBetta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Nemo Betta</t>
-        </is>
-      </c>
-      <c r="D7" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4">
-        <v>0.55</v>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -3851,40 +4976,56 @@
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat</t>
+          <t xml:space="preserve">BlueWildBetta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Koi</t>
-        </is>
-      </c>
-      <c r="D8" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0.55</v>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -3920,52 +5061,76 @@
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PlakatGalaxy</t>
+          <t xml:space="preserve">ColorfulBetta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
-        </is>
-      </c>
-      <c r="D9" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="J9" s="4">
-        <v>0.35</v>
-      </c>
-      <c r="K9" s="4">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4">
-        <v>1</v>
-      </c>
-      <c r="M9" s="4">
-        <v>0.35</v>
-      </c>
-      <c r="N9" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="O9" s="4">
-        <v>1.12</v>
+          <t xml:space="preserve">Colorful Betta</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
@@ -3981,15 +5146,15 @@
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedSteelBetta</t>
+          <t xml:space="preserve">GalaxyBetta</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Galaxy Betta</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -4066,15 +5231,15 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RoyalKoiBetta</t>
+          <t xml:space="preserve">GoldTigerBetta</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Betta Hổ Vàng</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4151,15 +5316,15 @@
     <row r="12" ht="66" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">KoiBetta</t>
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Koi Betta</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -4172,10 +5337,8 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="F12" s="4">
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -4236,83 +5399,792 @@
     <row r="13" ht="66" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">KoiNemoRig</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi Nemo Betta</t>
+        </is>
+      </c>
+      <c r="D13" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0.55</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NemoKoiBetta</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nemo Koi Betta</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Koi</t>
+        </is>
+      </c>
+      <c r="D15" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0.55</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PlakatGalaxy</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Galaxy</t>
+        </is>
+      </c>
+      <c r="D16" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="N16" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="O16" s="4">
+        <v>1.12</v>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PurpleRubyBetta</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedSteelBetta</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Steel Betta</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoyalKoiBetta</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Royal Koi</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkyKoiBetta</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
-      <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B21" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TealWhiteBetta</t>
+        </is>
+      </c>
+      <c r="B22" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4500,15 +6372,15 @@
     <row r="4" ht="66" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueFlameBetta</t>
+          <t xml:space="preserve">BlackSamuraiBetta</t>
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=a27d27b2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Samurai Đen</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -4560,15 +6432,15 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GalaxyBetta</t>
+          <t xml:space="preserve">BlueBeeBetta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=e09ffc42")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galaxy Betta</t>
+          <t xml:space="preserve">Betta Ong Xanh</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4620,15 +6492,15 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiBetta</t>
+          <t xml:space="preserve">BlueFlameBetta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=2cf7446e")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Betta</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4680,25 +6552,31 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KoiNemoRig</t>
+          <t xml:space="preserve">BluePandaBetta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Nemo Betta</t>
-        </is>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1.2</v>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -4710,45 +6588,55 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" s="4">
-        <v>0.6</v>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.55, 1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3, 0.8</t>
-        </is>
-      </c>
-      <c r="L7" s="4">
-        <v>0.55</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat</t>
+          <t xml:space="preserve">BlueWildBetta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Koi</t>
-        </is>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1.2</v>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -4760,81 +6648,99 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" s="4">
-        <v>0.6</v>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.55, 1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3, 0.8</t>
-        </is>
-      </c>
-      <c r="L8" s="4">
-        <v>0.55</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PlakatGalaxy</t>
+          <t xml:space="preserve">ColorfulBetta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=9a32eee1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
-        </is>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1.8</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0.6</v>
+          <t xml:space="preserve">Colorful Betta</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.55, 1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3, 0.8</t>
-        </is>
-      </c>
-      <c r="L9" s="4">
-        <v>0.72</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedSteelBetta</t>
+          <t xml:space="preserve">GalaxyBetta</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=874eae50")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Galaxy Betta</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -4886,15 +6792,15 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RoyalKoiBetta</t>
+          <t xml:space="preserve">GoldTigerBetta</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=01a07ba4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Betta Hổ Vàng</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4946,15 +6852,15 @@
     <row r="12" ht="66" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">KoiBetta</t>
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=cfb374af")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Koi Betta</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -5006,58 +6912,564 @@
     <row r="13" ht="66" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">KoiNemoRig</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Koi Nemo Betta</t>
+        </is>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.55, 1</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.3, 0.8</t>
+        </is>
+      </c>
+      <c r="L13" s="4">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NemoKoiBetta</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nemo Koi Betta</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Koi</t>
+        </is>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I15" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.55, 1</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.3, 0.8</t>
+        </is>
+      </c>
+      <c r="L15" s="4">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PlakatGalaxy</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plakat Galaxy</t>
+        </is>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.55, 1</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.3, 0.8</t>
+        </is>
+      </c>
+      <c r="L16" s="4">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PurpleRubyBetta</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedSteelBetta</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Steel Betta</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoyalKoiBetta</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Royal Koi</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkyKoiBetta</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Koi Betta</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
-      <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=0fd7b315")</f>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B21" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TealWhiteBetta</t>
+        </is>
+      </c>
+      <c r="B22" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/Sheets/decor_catalog.xlsx
+++ b/Sheets/decor_catalog.xlsx
@@ -424,7 +424,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/hornwort.png?v=6f439db3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/hornwort.png?v=e4098bc0")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/cabomba.png?v=2521a16b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/cabomba.png?v=a4c09fc0")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/vallisneria.png?v=eea77be9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/vallisneria.png?v=396e176d")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/rotala.png?v=78de231a")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/rotala.png?v=1600b205")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/anubias-petite.png?v=931b9c16")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/anubias-petite.png?v=30b5a2fa")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/java-fern.png?v=9636ccba")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/java-fern.png?v=6c5c92cf")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/starter-anubias.png?v=a9eaf0b3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/starter-anubias.png?v=c6288cfa")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/vallisneria-tall.png?v=ca47d4e7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/vallisneria-tall.png?v=a37bd736")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/rotala-tall.png?v=5f775dea")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/rotala-tall.png?v=70074055")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/amazon-sword.png?v=f28ab0f3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/amazon-sword.png?v=8692bbc2")</f>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -725,6 +725,316 @@
       </c>
       <c r="G11" s="3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ludwigia-red</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/ludwigia-red.png?v=23cc607d")</f>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rau mương đỏ Super Red</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bụi thân đứng, lá tròn chuyển từ xanh sang đỏ rượu ở ngọn · Trồng hậu cảnh · 1 điểm</t>
+        </is>
+      </c>
+      <c r="E12" s="4">
+        <v>150</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.30 × 1.05 × 0.35</t>
+        </is>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">water-wisteria</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/water-wisteria.png?v=8146d316")</f>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thuỷ cúc</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lá xẻ thuỳ như ren, xanh non · Trồng hậu cảnh · 1 điểm</t>
+        </is>
+      </c>
+      <c r="E13" s="4">
+        <v>110</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.39 × 0.86 × 0.37</t>
+        </is>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anubias-hammock</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/anubias-hammock.png?v=9729f156")</f>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ráy lá võng</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Một lá to nằm ngang gần mặt nước cho betta nghỉ · Hậu, trung cảnh · 1 điểm</t>
+        </is>
+      </c>
+      <c r="E14" s="4">
+        <v>160</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.42 × 0.89 × 0.23</t>
+        </is>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tiger-lotus-red</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/tiger-lotus-red.png?v=df0ae515")</f>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Súng hổ đỏ</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bụi lá đỏ tía có vân, thêm lá súng vươn lên gần mặt nước · Điểm nhấn trung cảnh · 2 điểm</t>
+        </is>
+      </c>
+      <c r="E15" s="4">
+        <v>260</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.71 × 1.72 × 0.60</t>
+        </is>
+      </c>
+      <c r="G15" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madagascar-lace</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/madagascar-lace.png?v=a11ccf37")</f>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lưới Madagascar</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lá dài như tấm lưới đan, nhìn xuyên qua được · Cây hiếm cho trung cảnh · 2 điểm</t>
+        </is>
+      </c>
+      <c r="E16" s="4">
+        <v>320</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.57 × 0.39 × 0.47</t>
+        </is>
+      </c>
+      <c r="G16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crypt-wendtii</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/crypt-wendtii.png?v=4c7a6291")</f>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ráy Crypt nâu</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bụi lá thuôn mép gợn sóng màu đồng nâu · Trung cảnh · 1 điểm</t>
+        </is>
+      </c>
+      <c r="E17" s="4">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.27 × 0.21 × 0.21</t>
+        </is>
+      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alternanthera-mini</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/alternanthera-mini.png?v=884ec291")</f>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huyết tâm lan mini</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bụi rậm lá nhỏ hồng đỏ · Thêm màu ấm giữa hồ · 1 điểm</t>
+        </is>
+      </c>
+      <c r="E18" s="4">
+        <v>130</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.21 × 0.19 × 0.21</t>
+        </is>
+      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bucephalandra</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/bucephalandra.png?v=02901a05")</f>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ráy Buce xanh ánh kim</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lá nhỏ xanh thẫm ánh xanh dương, lá non đỏ nâu · Trồng trên nền hoặc kéo lên lũa, đá để gắn</t>
+        </is>
+      </c>
+      <c r="E19" s="4">
+        <v>140</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.11 × 0.06 × 0.06</t>
+        </is>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">downoi</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/downoi.png?v=93c51ee0")</f>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downoi lá xoăn</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các cụm hoa thị nhỏ lá xoăn xanh tươi · Trồng tiền cảnh</t>
+        </is>
+      </c>
+      <c r="E20" s="4">
+        <v>90</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.19 × 0.01 × 0.18</t>
+        </is>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mosaic-plant</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/mosaic-plant.png?v=1d3109c4")</f>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bèo khảm đỏ</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thân dài từ đáy, nở hoa thị lá hình thoi như tranh khảm gần mặt nước · 1 điểm</t>
+        </is>
+      </c>
+      <c r="E21" s="4">
+        <v>190</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.47 × 1.74 × 0.49</t>
+        </is>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -787,7 +1097,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/java-moss.png?v=4296be1f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/java-moss.png?v=5cda24f3")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -800,7 +1110,7 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -818,7 +1128,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/christmas-moss.png?v=bec1ee5a")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/christmas-moss.png?v=d1f42300")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -831,7 +1141,7 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -849,7 +1159,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/mini-fiss.png?v=ab3fa96d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/mini-fiss.png?v=dff72601")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -862,7 +1172,7 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -880,7 +1190,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/moss-mini-taiwan.png?v=6278abc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/moss-mini-taiwan.png?v=c8884ab5")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -893,7 +1203,7 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -911,7 +1221,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/moss-weeping.png?v=aa4174f8")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/moss-weeping.png?v=e0949b6b")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -924,7 +1234,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -942,7 +1252,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/moss-flame.png?v=22f039a3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/moss-flame.png?v=38fe3e77")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -955,7 +1265,7 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -969,90 +1279,90 @@
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">moss-wall-taiwan</t>
+          <t xml:space="preserve">carpet-hairgrass</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/moss-wall-taiwan.png?v=ebebe697")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/carpet-hairgrass.png?v=1733b7a6")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tường rêu Mini Taiwan</t>
+          <t xml:space="preserve">Thảm Ngưu mao chiên</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tấm rêu dán kính sau hồ, phủ thảm dày · Ghép nhiều tấm thành tường rêu</t>
+          <t xml:space="preserve">Gói 10 ô thảm tiền cảnh · Chọn rồi kéo trên cát để trải, Tẩy để xoá · Không tính điểm</t>
         </is>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.44 × 0.34 × 0.03</t>
+          <t xml:space="preserve">0.23 × 0.09 × 0.16</t>
         </is>
       </c>
       <c r="G8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">moss-wall-weeping</t>
+          <t xml:space="preserve">carpet-monte-carlo</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/moss-wall-weeping.png?v=660d745e")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/carpet-monte-carlo.png?v=e41eea7c")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tường rêu Weeping</t>
+          <t xml:space="preserve">Thảm Trân châu Nhật</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tấm rêu dán kính sau hồ, nhánh rủ xuống như thác · Ghép nhiều tấm thành tường rêu</t>
+          <t xml:space="preserve">Gói 10 ô thảm tiền cảnh · Chọn rồi kéo trên cát để trải, Tẩy để xoá · Không tính điểm</t>
         </is>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45 × 0.32 × 0.11</t>
+          <t xml:space="preserve">0.21 × 0.03 × 0.14</t>
         </is>
       </c>
       <c r="G9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">carpet-hairgrass</t>
+          <t xml:space="preserve">carpet-hc-cuba</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/carpet-hairgrass.png?v=fe03e6ad")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/carpet-hc-cuba.png?v=d97430da")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thảm Ngưu mao chiên</t>
+          <t xml:space="preserve">Thảm Trân châu Cuba</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gói 10 ô thảm tiền cảnh · Chọn rồi kéo trên cát để trải, Tẩy để xoá · Không tính điểm</t>
+          <t xml:space="preserve">Lá li ti xanh non phủ kín như nhung · Gói 10 ô · Kéo trên cát, lũa, đá hoặc kính sau để trải, Tẩy để xoá · Không tính điểm</t>
         </is>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.23 × 0.09 × 0.16</t>
+          <t xml:space="preserve">0.21 × 0.01 × 0.14</t>
         </is>
       </c>
       <c r="G10" s="3">
@@ -1062,31 +1372,93 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">carpet-monte-carlo</t>
+          <t xml:space="preserve">carpet-java-moss</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/carpet-monte-carlo.png?v=4c898d13")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/carpet-java-moss.png?v=d3c60282")</f>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thảm Trân châu Nhật</t>
+          <t xml:space="preserve">Thảm rêu Java</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gói 10 ô thảm tiền cảnh · Chọn rồi kéo trên cát để trải, Tẩy để xoá · Không tính điểm</t>
+          <t xml:space="preserve">Rêu lông vũ xanh đậm bò sát mặt lũa, đá · Gói 10 ô · Kéo trên cát, lũa, đá hoặc kính sau để trải, Tẩy để xoá · Không tính điểm</t>
         </is>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.21 × 0.03 × 0.14</t>
+          <t xml:space="preserve">0.24 × 0.00 × 0.17</t>
         </is>
       </c>
       <c r="G11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carpet-riccia</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/carpet-riccia.png?v=cdd4d0c2")</f>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thảm rêu Riccia</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tản rêu chẻ nhánh xanh chanh, bám đá thành đệm · Gói 10 ô · Kéo trên cát, lũa, đá hoặc kính sau để trải, Tẩy để xoá · Không tính điểm</t>
+        </is>
+      </c>
+      <c r="E12" s="4">
+        <v>75</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.24 × 0.01 × 0.16</t>
+        </is>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carpet-marimo</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/carpet-marimo.png?v=4bc73a3d")</f>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thảm tảo Marimo</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tảo cầu xanh thẫm mọc thành đệm tròn mịn · Gói 10 ô · Kéo trên cát, lũa, đá hoặc kính sau để trải, Tẩy để xoá · Không tính điểm</t>
+        </is>
+      </c>
+      <c r="E13" s="4">
+        <v>90</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.20 × 0.01 × 0.13</t>
+        </is>
+      </c>
+      <c r="G13" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1150,7 +1522,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/duckweed.png?v=4e79067c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/duckweed.png?v=cffbdff3")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -1163,7 +1535,7 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -1181,7 +1553,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/salvinia.png?v=85d01fb4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/salvinia.png?v=e72ba8af")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -1194,7 +1566,7 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1212,7 +1584,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/frogbit.png?v=c89b8d11")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/frogbit.png?v=f0f4d049")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -1225,14 +1597,76 @@
         </is>
       </c>
       <c r="E4" s="4">
+        <v>70</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.22 × 0.15 × 0.16</t>
+        </is>
+      </c>
+      <c r="G4" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.22 × 0.15 × 0.16</t>
-        </is>
-      </c>
-      <c r="G4" s="3">
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red-root-floater</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/red-root-floater.png?v=af905907")</f>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bèo rễ đỏ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lá tròn nhỏ đỏ, rễ đỏ buông xuống nước · Kéo để sắp xếp từng cụm</t>
+        </is>
+      </c>
+      <c r="E5" s="4">
+        <v>70</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.19 × 0.06 × 0.19</t>
+        </is>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">water-lettuce</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/water-lettuce.png?v=7dbfeb6e")</f>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bèo cái mini</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hoa thị lá nhung có gân, rễ tua dài, tạo bóng râm cho betta · Kéo để sắp xếp từng cụm</t>
+        </is>
+      </c>
+      <c r="E6" s="4">
+        <v>80</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.20 × 0.16 × 0.17</t>
+        </is>
+      </c>
+      <c r="G6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1297,7 +1731,7 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
@@ -1320,7 +1754,7 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
@@ -1343,7 +1777,7 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
@@ -1366,7 +1800,7 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
@@ -1389,7 +1823,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
@@ -1412,7 +1846,237 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_basalt</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_basalt.png?v=5d8a9b1f")</f>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đá núi lửa đen</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách đá núi lửa đen với khe nứt tự nhiên</t>
+        </is>
+      </c>
+      <c r="E8" s="4">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_limestone</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_limestone.png?v=09876e4e")</f>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đá vôi trắng</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách đá vôi trắng ngà với hốc đá mềm mại</t>
+        </is>
+      </c>
+      <c r="E9" s="4">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_sandstone</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_sandstone.png?v=a6b2f585")</f>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sa thạch phân tầng</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách sa thạch vàng cam với vân đá uốn lượn</t>
+        </is>
+      </c>
+      <c r="E10" s="4">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_amazon_roots</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_amazon_roots.png?v=82697650")</f>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rễ cây Amazon</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách rễ cây nâu đan xen như rừng ngập nước</t>
+        </is>
+      </c>
+      <c r="E11" s="4">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_frosted_aqua</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_frosted_aqua.png?v=5c556703")</f>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kính mờ xanh sương</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách kính mờ xanh ngọc nhạt dịu mắt</t>
+        </is>
+      </c>
+      <c r="E12" s="4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_matte_black</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_matte_black.png?v=e777a8e3")</f>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đen nhám</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách đen nhám tối giản làm nổi bật màu cá</t>
+        </is>
+      </c>
+      <c r="E13" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_dragon_stone</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_dragon_stone.png?v=bc1e11b5")</f>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đá rồng</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách đá rồng màu đất với nhiều hốc phong hóa</t>
+        </is>
+      </c>
+      <c r="E14" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_pearl_marble</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_pearl_marble.png?v=044bf7a8")</f>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cẩm thạch ngọc trai</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách cẩm thạch trắng kem với đường vân thanh mảnh</t>
+        </is>
+      </c>
+      <c r="E15" s="4">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_turquoise_mosaic</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_turquoise_mosaic.png?v=6f44d7c7")</f>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mosaic xanh ngọc</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách gạch mosaic xanh ngọc với mạch gạch màu kem</t>
+        </is>
+      </c>
+      <c r="E16" s="4">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wall_sunken_relic</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/surface/surface_wall_sunken_relic.png?v=936ca725")</f>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Di tích chìm</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vách đá cổ chạm khắc hình học phủ rêu nhẹ</t>
+        </is>
+      </c>
+      <c r="E17" s="4">
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -1476,7 +2140,7 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
@@ -1499,7 +2163,7 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
@@ -1522,7 +2186,7 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
@@ -1545,7 +2209,7 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
@@ -1568,7 +2232,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
@@ -1591,7 +2255,7 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -1665,7 +2329,7 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -1694,7 +2358,7 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1723,7 +2387,7 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1794,7 +2458,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -1807,7 +2471,7 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -1827,7 +2491,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -1840,7 +2504,7 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1860,7 +2524,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -1873,7 +2537,7 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1893,7 +2557,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -1906,7 +2570,7 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1926,7 +2590,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -1939,7 +2603,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1959,7 +2623,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -1972,7 +2636,7 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1992,7 +2656,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -2005,7 +2669,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2025,7 +2689,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -2038,7 +2702,7 @@
         </is>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2058,7 +2722,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -2071,7 +2735,7 @@
         </is>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2091,7 +2755,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -2104,7 +2768,7 @@
         </is>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2124,7 +2788,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -2137,7 +2801,7 @@
         </is>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2157,7 +2821,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -2170,7 +2834,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2190,7 +2854,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -2203,7 +2867,7 @@
         </is>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2223,7 +2887,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -2236,7 +2900,7 @@
         </is>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2256,7 +2920,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -2269,7 +2933,7 @@
         </is>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2289,7 +2953,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -2302,7 +2966,7 @@
         </is>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2322,7 +2986,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -2335,7 +2999,7 @@
         </is>
       </c>
       <c r="E18" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2355,7 +3019,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -2368,7 +3032,7 @@
         </is>
       </c>
       <c r="E19" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2388,7 +3052,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -2401,7 +3065,7 @@
         </is>
       </c>
       <c r="E20" s="4">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2409,6 +3073,39 @@
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yellow-koi-betta</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Koi Vàng</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thân vàng cam đốm xanh, đuôi vàng chuyển trắng xanh · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E21" s="4">
+        <v>1400</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1.5</t>
         </is>
@@ -2564,7 +3261,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -2609,7 +3306,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -2654,7 +3351,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -2699,7 +3396,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -2744,7 +3441,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -2789,7 +3486,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -2834,7 +3531,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -2879,7 +3576,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -2924,7 +3621,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -2969,7 +3666,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -3006,7 +3703,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -3051,7 +3748,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -3088,7 +3785,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -3125,7 +3822,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -3170,7 +3867,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -3215,7 +3912,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
@@ -3260,7 +3957,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -3305,7 +4002,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -3350,7 +4047,7 @@
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
@@ -3383,6 +4080,51 @@
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YellowKoiBetta</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Koi Vàng</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3554,7 +4296,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -3599,7 +4341,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -3644,7 +4386,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -3689,7 +4431,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -3734,7 +4476,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -3779,7 +4521,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -3824,7 +4566,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -3869,7 +4611,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -3914,7 +4656,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -3959,7 +4701,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -4004,7 +4746,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -4049,7 +4791,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -4094,7 +4836,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -4139,7 +4881,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -4184,7 +4926,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -4229,7 +4971,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
@@ -4274,7 +5016,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -4319,7 +5061,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -4364,7 +5106,7 @@
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
@@ -4397,6 +5139,51 @@
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YellowKoiBetta</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Koi Vàng</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4640,7 +5427,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -4725,7 +5512,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -4810,7 +5597,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -4895,7 +5682,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -4980,7 +5767,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -5065,7 +5852,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -5150,7 +5937,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -5235,7 +6022,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -5320,7 +6107,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -5403,7 +6190,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -5472,7 +6259,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -5557,7 +6344,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -5626,7 +6413,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -5687,7 +6474,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -5772,7 +6559,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -5857,7 +6644,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
@@ -5942,7 +6729,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -6027,7 +6814,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -6112,7 +6899,7 @@
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
@@ -6185,6 +6972,91 @@
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YellowKoiBetta</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Koi Vàng</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6376,7 +7248,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=b549c88d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -6436,7 +7308,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=85bff0c2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -6496,7 +7368,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=61739c12")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -6556,7 +7428,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=a4e582f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -6616,7 +7488,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=a11ef600")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -6676,7 +7548,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=6fc24bc4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -6736,7 +7608,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=048da540")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -6796,7 +7668,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=991b48ab")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -6856,7 +7728,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=8aae5c9b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -6916,7 +7788,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=4179f011")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -6966,7 +7838,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=93c8edc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -7026,7 +7898,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d93738a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -7076,7 +7948,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=ae7cef0c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -7122,7 +7994,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=c29de39f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -7182,7 +8054,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=2324212d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -7242,7 +8114,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=f17b64b7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
@@ -7302,7 +8174,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=006b22f9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -7362,7 +8234,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=cefa9890")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -7422,7 +8294,7 @@
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=45c3ab1c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
@@ -7470,6 +8342,66 @@
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YellowKoiBetta</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Koi Vàng</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7535,7 +8467,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-short.png?v=452443f5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-short.png?v=9cb581d6")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -7548,11 +8480,11 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.31 × 0.23 × 0.10</t>
+          <t xml:space="preserve">0.32 × 0.12 × 0.20</t>
         </is>
       </c>
       <c r="G2" s="3">
@@ -7566,7 +8498,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-long.png?v=301f005f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-long.png?v=1735bbac")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -7579,11 +8511,11 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.56 × 0.23 × 0.11</t>
+          <t xml:space="preserve">0.74 × 0.25 × 0.34</t>
         </is>
       </c>
       <c r="G3" s="3">
@@ -7597,7 +8529,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-arch.png?v=d09d80c4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-arch.png?v=706da181")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -7610,11 +8542,11 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45 × 0.35 × 0.09</t>
+          <t xml:space="preserve">0.75 × 0.28 × 0.25</t>
         </is>
       </c>
       <c r="G4" s="3">
@@ -7628,7 +8560,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-branches.png?v=6f47e2e2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-branches.png?v=e6c8a6d2")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -7641,11 +8573,11 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.36 × 0.45 × 0.27</t>
+          <t xml:space="preserve">0.29 × 0.43 × 0.17</t>
         </is>
       </c>
       <c r="G5" s="3">
@@ -7659,7 +8591,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-roots.png?v=a1fc8381")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-roots.png?v=ea4ef16e")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -7672,11 +8604,11 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.36 × 0.45 × 0.30</t>
+          <t xml:space="preserve">0.38 × 0.38 × 0.40</t>
         </is>
       </c>
       <c r="G6" s="3">
@@ -7690,7 +8622,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-stump.png?v=ba1175c2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-stump.png?v=a984c7ad")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -7703,11 +8635,11 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.36 × 0.34 × 0.27</t>
+          <t xml:space="preserve">0.27 × 0.29 × 0.28</t>
         </is>
       </c>
       <c r="G7" s="3">
@@ -7721,7 +8653,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-linh-sam.png?v=bcb8faa2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-linh-sam.png?v=0ef0d520")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -7734,11 +8666,11 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.53 × 0.50 × 0.25</t>
+          <t xml:space="preserve">0.55 × 0.52 × 0.30</t>
         </is>
       </c>
       <c r="G8" s="3">
@@ -7752,7 +8684,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-hai-son-tung.png?v=155b614c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-hai-son-tung.png?v=260e165d")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -7765,7 +8697,7 @@
         </is>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -7783,7 +8715,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-do-quyen.png?v=63db7473")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-do-quyen.png?v=85838f52")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -7796,7 +8728,7 @@
         </is>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -7814,7 +8746,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-spider.png?v=d4963d3d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-spider.png?v=bf740eaa")</f>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -7827,7 +8759,7 @@
         </is>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -7845,7 +8777,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-san-da.png?v=4076d2e4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-san-da.png?v=6004c25c")</f>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -7858,11 +8790,11 @@
         </is>
       </c>
       <c r="E12" s="4">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.43 × 0.55 × 0.39</t>
+          <t xml:space="preserve">0.37 × 0.52 × 0.34</t>
         </is>
       </c>
       <c r="G12" s="3">
@@ -7876,7 +8808,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-mopani.png?v=fe261d46")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-mopani.png?v=3e1decf6")</f>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -7889,11 +8821,11 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.30 × 0.30 × 0.20</t>
+          <t xml:space="preserve">0.29 × 0.37 × 0.29</t>
         </is>
       </c>
       <c r="G13" s="3">
@@ -7907,7 +8839,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-tra-gung.png?v=13fd1786")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-tra-gung.png?v=f0ddf9d2")</f>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -7920,7 +8852,7 @@
         </is>
       </c>
       <c r="E14" s="4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -7938,7 +8870,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-bonsai.png?v=b1f373e5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-bonsai.png?v=2b774f12")</f>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -7951,7 +8883,7 @@
         </is>
       </c>
       <c r="E15" s="4">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -7969,7 +8901,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/starter-wood.png?v=d7dc4fcb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/starter-wood.png?v=4c64cdf0")</f>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -7982,11 +8914,11 @@
         </is>
       </c>
       <c r="E16" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.42 × 0.68 × 0.23</t>
+          <t xml:space="preserve">0.48 × 0.62 × 0.38</t>
         </is>
       </c>
       <c r="G16" s="3">
@@ -8000,7 +8932,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-linh-sam-m.png?v=4fc56be2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-linh-sam-m.png?v=a6e6d293")</f>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -8013,11 +8945,11 @@
         </is>
       </c>
       <c r="E17" s="4">
-        <v>1</v>
+        <v>440</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95 × 0.90 × 0.45</t>
+          <t xml:space="preserve">1.00 × 0.94 × 0.53</t>
         </is>
       </c>
       <c r="G17" s="3">
@@ -8031,7 +8963,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-linh-sam-l.png?v=f1401a84")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-linh-sam-l.png?v=be3957c2")</f>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -8044,11 +8976,11 @@
         </is>
       </c>
       <c r="E18" s="4">
-        <v>1</v>
+        <v>770</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.20 × 1.14 × 0.58</t>
+          <t xml:space="preserve">1.20 × 1.13 × 0.64</t>
         </is>
       </c>
       <c r="G18" s="3">
@@ -8062,7 +8994,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-hai-son-tung-m.png?v=dd1c0119")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-hai-son-tung-m.png?v=a597127b")</f>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -8075,7 +9007,7 @@
         </is>
       </c>
       <c r="E19" s="4">
-        <v>1</v>
+        <v>480</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -8093,7 +9025,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-hai-son-tung-l.png?v=b703b3ae")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-hai-son-tung-l.png?v=b8e06263")</f>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -8106,7 +9038,7 @@
         </is>
       </c>
       <c r="E20" s="4">
-        <v>1</v>
+        <v>840</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -8124,7 +9056,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-do-quyen-m.png?v=1d5335f7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-do-quyen-m.png?v=3eaa4377")</f>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -8137,7 +9069,7 @@
         </is>
       </c>
       <c r="E21" s="4">
-        <v>1</v>
+        <v>460</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -8155,7 +9087,7 @@
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-do-quyen-l.png?v=e37d1a90")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-do-quyen-l.png?v=06d44b64")</f>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -8168,7 +9100,7 @@
         </is>
       </c>
       <c r="E22" s="4">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -8186,7 +9118,7 @@
         </is>
       </c>
       <c r="B23" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-spider-m.png?v=f49a403b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-spider-m.png?v=97cd6d86")</f>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -8199,7 +9131,7 @@
         </is>
       </c>
       <c r="E23" s="4">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -8217,7 +9149,7 @@
         </is>
       </c>
       <c r="B24" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-spider-l.png?v=0f89b8ba")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-spider-l.png?v=382569b6")</f>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -8230,7 +9162,7 @@
         </is>
       </c>
       <c r="E24" s="4">
-        <v>1</v>
+        <v>670</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -8248,7 +9180,7 @@
         </is>
       </c>
       <c r="B25" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-san-da-m.png?v=30be2b65")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-san-da-m.png?v=042aa04d")</f>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -8261,11 +9193,11 @@
         </is>
       </c>
       <c r="E25" s="4">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.77 × 1.00 × 0.70</t>
+          <t xml:space="preserve">0.66 × 0.94 × 0.60</t>
         </is>
       </c>
       <c r="G25" s="3">
@@ -8279,7 +9211,7 @@
         </is>
       </c>
       <c r="B26" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-san-da-l.png?v=bd31ded2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-san-da-l.png?v=89746928")</f>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -8292,11 +9224,11 @@
         </is>
       </c>
       <c r="E26" s="4">
-        <v>1</v>
+        <v>880</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.20 × 1.56 × 1.09</t>
+          <t xml:space="preserve">1.10 × 1.57 × 1.01</t>
         </is>
       </c>
       <c r="G26" s="3">
@@ -8310,7 +9242,7 @@
         </is>
       </c>
       <c r="B27" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-mopani-m.png?v=a433357b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-mopani-m.png?v=180775a1")</f>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -8323,11 +9255,11 @@
         </is>
       </c>
       <c r="E27" s="4">
-        <v>1</v>
+        <v>520</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.54 × 0.54 × 0.37</t>
+          <t xml:space="preserve">0.52 × 0.66 × 0.52</t>
         </is>
       </c>
       <c r="G27" s="3">
@@ -8341,7 +9273,7 @@
         </is>
       </c>
       <c r="B28" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-mopani-l.png?v=02600ee7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-mopani-l.png?v=60e7e90b")</f>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -8354,11 +9286,11 @@
         </is>
       </c>
       <c r="E28" s="4">
-        <v>1</v>
+        <v>910</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.90 × 0.90 × 0.61</t>
+          <t xml:space="preserve">0.86 × 1.10 × 0.86</t>
         </is>
       </c>
       <c r="G28" s="3">
@@ -8372,7 +9304,7 @@
         </is>
       </c>
       <c r="B29" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-tra-gung-m.png?v=f1410912")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-tra-gung-m.png?v=f62605cd")</f>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -8385,7 +9317,7 @@
         </is>
       </c>
       <c r="E29" s="4">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -8403,7 +9335,7 @@
         </is>
       </c>
       <c r="B30" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-tra-gung-l.png?v=1de3c040")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-tra-gung-l.png?v=c8dfda69")</f>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -8416,7 +9348,7 @@
         </is>
       </c>
       <c r="E30" s="4">
-        <v>1</v>
+        <v>420</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -8434,7 +9366,7 @@
         </is>
       </c>
       <c r="B31" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-bonsai-m.png?v=05394b90")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-bonsai-m.png?v=8eda70da")</f>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -8447,7 +9379,7 @@
         </is>
       </c>
       <c r="E31" s="4">
-        <v>1</v>
+        <v>640</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -8465,7 +9397,7 @@
         </is>
       </c>
       <c r="B32" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-bonsai-l.png?v=5e93f602")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-bonsai-l.png?v=549bcaea")</f>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -8478,7 +9410,7 @@
         </is>
       </c>
       <c r="E32" s="4">
-        <v>1</v>
+        <v>1120</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -8496,7 +9428,7 @@
         </is>
       </c>
       <c r="B33" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-co-thu.png?v=ad816b5d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/wood-co-thu.png?v=538845df")</f>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
@@ -8509,11 +9441,11 @@
         </is>
       </c>
       <c r="E33" s="4">
-        <v>1</v>
+        <v>900</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.49 × 1.71 × 0.58</t>
+          <t xml:space="preserve">0.96 × 1.89 × 1.01</t>
         </is>
       </c>
       <c r="G33" s="3">
@@ -8580,7 +9512,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/river-pebbles.png?v=97f2c564")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/river-pebbles.png?v=959cabfc")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -8593,11 +9525,11 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.42 × 0.14 × 0.33</t>
+          <t xml:space="preserve">0.30 × 0.08 × 0.24</t>
         </is>
       </c>
       <c r="G2" s="3">
@@ -8611,7 +9543,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/dragon-stone.png?v=24629cae")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/dragon-stone.png?v=b8c925af")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -8624,11 +9556,11 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.28 × 0.68 × 0.28</t>
+          <t xml:space="preserve">0.40 × 0.26 × 0.28</t>
         </is>
       </c>
       <c r="G3" s="3">
@@ -8642,7 +9574,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/lava-rock.png?v=260fd948")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/lava-rock.png?v=759be537")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -8655,11 +9587,11 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.43 × 0.39 × 0.41</t>
+          <t xml:space="preserve">0.29 × 0.15 × 0.28</t>
         </is>
       </c>
       <c r="G4" s="3">
@@ -8673,7 +9605,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/seiryu.png?v=7de1eaf5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/seiryu.png?v=5b643a00")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -8686,11 +9618,11 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.41 × 0.55 × 0.36</t>
+          <t xml:space="preserve">0.30 × 0.35 × 0.24</t>
         </is>
       </c>
       <c r="G5" s="3">
@@ -8704,7 +9636,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/rock-cluster.png?v=17848b11")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/rock-cluster.png?v=ae292627")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -8717,11 +9649,11 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.49 × 0.55 × 0.42</t>
+          <t xml:space="preserve">0.40 × 0.35 × 0.22</t>
         </is>
       </c>
       <c r="G6" s="3">
@@ -8735,7 +9667,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/mini-landscape.png?v=262b065a")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/mini-landscape.png?v=3ab59a3f")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -8748,11 +9680,11 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.51 × 0.63 × 0.29</t>
+          <t xml:space="preserve">0.51 × 0.37 × 0.29</t>
         </is>
       </c>
       <c r="G7" s="3">
@@ -8766,7 +9698,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-elephant-skin.png?v=def74d81")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-elephant-skin.png?v=0f98ef22")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -8779,11 +9711,11 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.44 × 0.27 × 0.30</t>
+          <t xml:space="preserve">0.45 × 0.27 × 0.32</t>
         </is>
       </c>
       <c r="G8" s="3">
@@ -8797,7 +9729,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-coral-rock.png?v=130333c3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-coral-rock.png?v=f5629271")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -8810,7 +9742,7 @@
         </is>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -8828,7 +9760,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-lava-red.png?v=a98337af")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-lava-red.png?v=97049791")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -8841,7 +9773,7 @@
         </is>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -8859,7 +9791,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-sea-pebbles.png?v=732854d9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-sea-pebbles.png?v=97cc9a80")</f>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -8872,7 +9804,7 @@
         </is>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -8890,7 +9822,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-co-thach.png?v=9270d3a8")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-co-thach.png?v=e9385772")</f>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -8903,7 +9835,7 @@
         </is>
       </c>
       <c r="E12" s="4">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -8921,7 +9853,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-tuyet-son.png?v=c7fe40d7")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-tuyet-son.png?v=c37127a1")</f>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -8934,7 +9866,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -8952,7 +9884,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/starter-stone.png?v=0ba48c6c")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/starter-stone.png?v=5216b73e")</f>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -8983,7 +9915,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-elephant-skin-m.png?v=ca992955")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-elephant-skin-m.png?v=bdd534cc")</f>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -9000,7 +9932,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.80 × 0.49 × 0.54</t>
+          <t xml:space="preserve">0.81 × 0.49 × 0.58</t>
         </is>
       </c>
       <c r="G15" s="3">
@@ -9014,7 +9946,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-elephant-skin-l.png?v=233bb469")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-elephant-skin-l.png?v=bee8cc3b")</f>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -9031,7 +9963,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.20 × 0.73 × 0.81</t>
+          <t xml:space="preserve">1.20 × 0.72 × 0.86</t>
         </is>
       </c>
       <c r="G16" s="3">
@@ -9045,7 +9977,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-coral-rock-m.png?v=2c66a034")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-coral-rock-m.png?v=90485909")</f>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -9076,7 +10008,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-coral-rock-l.png?v=75ff3fd9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-coral-rock-l.png?v=63f9f653")</f>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -9107,7 +10039,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-lava-red-m.png?v=298ab498")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-lava-red-m.png?v=753ca2b1")</f>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -9138,7 +10070,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-lava-red-l.png?v=f370f3e2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-lava-red-l.png?v=42e279b9")</f>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -9169,7 +10101,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-sea-pebbles-m.png?v=7c9fb1ee")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-sea-pebbles-m.png?v=17e620d2")</f>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -9200,7 +10132,7 @@
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-sea-pebbles-l.png?v=fddf531b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-sea-pebbles-l.png?v=643d9c60")</f>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -9231,7 +10163,7 @@
         </is>
       </c>
       <c r="B23" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-co-thach-m.png?v=6b8bd51f")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-co-thach-m.png?v=ee68b9e0")</f>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -9262,7 +10194,7 @@
         </is>
       </c>
       <c r="B24" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-co-thach-l.png?v=ce17e38e")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-co-thach-l.png?v=e0e38b53")</f>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -9293,7 +10225,7 @@
         </is>
       </c>
       <c r="B25" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-tuyet-son-m.png?v=58d719a2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-tuyet-son-m.png?v=beaa4659")</f>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -9324,7 +10256,7 @@
         </is>
       </c>
       <c r="B26" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-tuyet-son-l.png?v=66f30b50")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-tuyet-son-l.png?v=42c422c9")</f>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -9355,7 +10287,7 @@
         </is>
       </c>
       <c r="B27" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-iwagumi.png?v=8ac3bb1b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-iwagumi.png?v=fcff3716")</f>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -9386,7 +10318,7 @@
         </is>
       </c>
       <c r="B28" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-slab.png?v=7cb8d94d")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-slab.png?v=72db9db4")</f>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -9417,7 +10349,7 @@
         </is>
       </c>
       <c r="B29" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-cliff.png?v=c96e455a")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/stone-cliff.png?v=c4d73946")</f>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -9501,7 +10433,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-rubble.png?v=b433013b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-rubble.png?v=4c0d926a")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -9514,7 +10446,7 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -9532,24 +10464,24 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-block.png?v=7ca277ee")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-block.png?v=4f764d03")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San hô khối</t>
+          <t xml:space="preserve">San hô não xanh vàng</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khối san hô thật vân não · Dùng cho bể nước mặn, giúp ổn định pH</t>
+          <t xml:space="preserve">Khối xanh ngọc với gân nổi uốn lượn màu vàng · Điểm nhấn tiền cảnh</t>
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.28 × 0.17 × 0.29</t>
+          <t xml:space="preserve">0.27 × 0.21 × 0.24</t>
         </is>
       </c>
       <c r="G3" s="3">
@@ -9563,24 +10495,24 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-mushroom.png?v=c5388742")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-mushroom.png?v=6d5205e1")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San hô nấm</t>
+          <t xml:space="preserve">San hô nấm xanh viền tím</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San hô sống bể biển, đĩa màu rực rỡ · Cần ánh sáng và dòng chảy chuyên dụng</t>
+          <t xml:space="preserve">Năm đĩa thịt xanh ngọc xếp cụm, gân tỏa và viền tím gợn sóng</t>
         </is>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.24 × 0.15 × 0.22</t>
+          <t xml:space="preserve">0.23 × 0.14 × 0.24</t>
         </is>
       </c>
       <c r="G4" s="3">
@@ -9594,24 +10526,24 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-zoanthid.png?v=5ad05353")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-zoanthid.png?v=32c5b38e")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San hô đồng tiền</t>
+          <t xml:space="preserve">San hô đồng tiền đa sắc</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cụm polyp tròn như đồng xu nhiều màu · San hô sống, cần ánh sáng và dòng chảy</t>
+          <t xml:space="preserve">Thảm polyp tâm cam, vòng xanh và tua tím · Phủ đá tiền cảnh</t>
         </is>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.26 × 0.11 × 0.23</t>
+          <t xml:space="preserve">0.23 × 0.12 × 0.24</t>
         </is>
       </c>
       <c r="G5" s="3">
@@ -9625,24 +10557,24 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-artificial-branch.png?v=b330ee0b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-artificial-branch.png?v=7d5c4244")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San hô nhân tạo nhánh</t>
+          <t xml:space="preserve">San hô sừng hươu hồng</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silicon an toàn, màu tươi, dễ vệ sinh · Mang phong cách biển vào hồ nước ngọt</t>
+          <t xml:space="preserve">Tán nhánh hồng đào dày, đầu kem · Đế đá sống tự nhiên</t>
         </is>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.33 × 0.20 × 0.31</t>
+          <t xml:space="preserve">0.28 × 0.27 × 0.34</t>
         </is>
       </c>
       <c r="G6" s="3">
@@ -9656,27 +10588,182 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-artificial-fan.png?v=101b0af4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-artificial-fan.png?v=9ca9f0f6")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San hô nhân tạo quạt</t>
+          <t xml:space="preserve">Quạt biển đỏ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quạt biển silicon mềm, màu tươi, dễ vệ sinh · Hợp người mới chơi và hồ nước ngọt</t>
+          <t xml:space="preserve">Quạt đỏ mảnh với mạng nhánh đan như ren · Điểm nhấn hậu cảnh</t>
         </is>
       </c>
       <c r="E7" s="4">
+        <v>130</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.50 × 0.48 × 0.19</t>
+        </is>
+      </c>
+      <c r="G7" s="3">
         <v>1</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.15 × 0.21 × 0.06</t>
-        </is>
-      </c>
-      <c r="G7" s="3">
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coral-plating</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-plating.png?v=125ca294")</f>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San hô đĩa tầng xanh ngọc</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiểu cảnh san hô 3D · Bộ mẫu đã duyệt</t>
+        </is>
+      </c>
+      <c r="E8" s="4">
+        <v>280</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.33 × 0.27 × 0.32</t>
+        </is>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coral-purple-branch</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-purple-branch.png?v=afde6820")</f>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San hô nhánh tím</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiểu cảnh san hô 3D · Bộ mẫu đã duyệt</t>
+        </is>
+      </c>
+      <c r="E9" s="4">
+        <v>260</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.21 × 0.24 × 0.26</t>
+        </is>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coral-torch</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-torch.png?v=4cd78453")</f>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San hô đuốc vàng</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiểu cảnh san hô 3D · Bộ mẫu đã duyệt</t>
+        </is>
+      </c>
+      <c r="E10" s="4">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.26 × 0.24 × 0.26</t>
+        </is>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coral-blue-tube</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-blue-tube.png?v=fc800238")</f>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San hô ống xanh</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiểu cảnh san hô 3D · Bộ mẫu đã duyệt</t>
+        </is>
+      </c>
+      <c r="E11" s="4">
+        <v>270</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.19 × 0.32 × 0.25</t>
+        </is>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coral-lobophyllia</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/decor/coral-lobophyllia.png?v=89fd7a69")</f>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San hô thịt hồng cam</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiểu cảnh san hô 3D · Bộ mẫu đã duyệt</t>
+        </is>
+      </c>
+      <c r="E12" s="4">
+        <v>290</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.21 × 0.14 × 0.23</t>
+        </is>
+      </c>
+      <c r="G12" s="3">
         <v>1</v>
       </c>
     </row>

--- a/Sheets/decor_catalog.xlsx
+++ b/Sheets/decor_catalog.xlsx
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=43252278")</f>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -2487,24 +2487,24 @@
     <row r="3" ht="66" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue-bee-betta</t>
+          <t xml:space="preserve">blue-flame-betta</t>
         </is>
       </c>
       <c r="B3" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9950f4a4")</f>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Ong Xanh</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đen xanh dương, khoang vàng · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Xanh dương, đỏ, cam · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E3" s="4">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2520,24 +2520,24 @@
     <row r="4" ht="66" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue-flame-betta</t>
+          <t xml:space="preserve">blue-panda-betta</t>
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=1cbc3e15")</f>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh dương, đỏ, cam · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Thân trắng hồng đốm đen, đuôi trắng mảng xanh dương đậm · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E4" s="4">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2553,24 +2553,24 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue-panda-betta</t>
+          <t xml:space="preserve">blue-wild-betta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=e36e243b")</f>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thân trắng hồng đốm đen, đuôi trắng mảng xanh dương đậm · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Betta hoang dã xanh lam, đốm đen trên vây · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E5" s="4">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2586,24 +2586,24 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue-wild-betta</t>
+          <t xml:space="preserve">colorful-betta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=5cc1541c")</f>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Rồng Xanh</t>
+          <t xml:space="preserve">Colorful Betta</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta hoang dã xanh lam, đốm đen trên vây · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Xanh dương, đỏ, trắng, vàng · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E6" s="4">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2619,24 +2619,24 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">colorful-betta</t>
+          <t xml:space="preserve">emerald-red-betta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/emerald-red-betta.png?v=c2d27f6b")</f>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colorful Betta</t>
+          <t xml:space="preserve">Betta Lục Bảo Đỏ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh dương, đỏ, trắng, vàng · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Thân vảy xanh lục bảo, vây đỏ viền sẫm, đuôi bán nguyệt · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E7" s="4">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=ab617dcf")</f>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b85cc880")</f>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=798a58a8")</f>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=f57fa2a7")</f>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=0a139958")</f>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d3f82500")</f>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=a66df8df")</f>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
+          <t xml:space="preserve">Koi Galaxy Betta</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi Galaxy: thân trắng ngọc mảng đỏ tươi, lưng vảy đen, mang trắng viền đỏ, vây vàng nghệ</t>
+          <t xml:space="preserve">Thân trắng ngọc mảng đỏ tươi, lưng vảy đen, mang trắng viền đỏ, vây vàng nghệ</t>
         </is>
       </c>
       <c r="E14" s="4">
@@ -2883,24 +2883,24 @@
     <row r="15" ht="66" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">purple-ruby-betta</t>
+          <t xml:space="preserve">purple-moon-betta</t>
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-moon-betta.png?v=f988dcb3")</f>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+          <t xml:space="preserve">Betta Trăng Tím</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thân tím hồng, đầu và vây đỏ hồng ngọc viền trắng · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Thân vảy bạc ánh kim, vây tím crôm, đuôi bán nguyệt viền trắng · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E15" s="4">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2916,24 +2916,24 @@
     <row r="16" ht="66" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">red-steel-betta</t>
+          <t xml:space="preserve">purple-ruby-betta</t>
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=8b2a77a6")</f>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thân xanh thép, vây đỏ trắng · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Thân tím hồng, đầu và vây đỏ hồng ngọc viền trắng · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E16" s="4">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2949,24 +2949,24 @@
     <row r="17" ht="66" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">royal-koi-betta</t>
+          <t xml:space="preserve">red-steel-betta</t>
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=e29f7895")</f>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Red Steel Betta</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koi xanh hoàng gia, đỏ, vàng · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Thân xanh thép, vây đỏ trắng · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E17" s="4">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2982,24 +2982,24 @@
     <row r="18" ht="66" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky-koi-betta</t>
+          <t xml:space="preserve">royal-koi-betta</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=413784be")</f>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanh da trời, đỏ, cam · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Koi xanh hoàng gia, đỏ, vàng · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E18" s="4">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3015,15 +3015,15 @@
     <row r="19" ht="66" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky-koi-betta-m4</t>
+          <t xml:space="preserve">sky-koi-betta</t>
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=974c7f77")</f>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta M4</t>
+          <t xml:space="preserve">Sky Koi Betta</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -3048,24 +3048,24 @@
     <row r="20" ht="66" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">teal-white-betta</t>
+          <t xml:space="preserve">sky-koi-betta-m4</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=099e8b9d")</f>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+          <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thân trắng, đuôi xanh ngọc lam, vây bụng cam · màu gốc theo mô hình</t>
+          <t xml:space="preserve">Xanh da trời, đỏ, cam · màu gốc theo mô hình</t>
         </is>
       </c>
       <c r="E20" s="4">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3081,31 +3081,64 @@
     <row r="21" ht="66" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">teal-white-betta</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=a25361f1")</f>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thân trắng, đuôi xanh ngọc lam, vây bụng cam · màu gốc theo mô hình</t>
+        </is>
+      </c>
+      <c r="E21" s="4">
+        <v>1300</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solid</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">yellow-koi-betta</t>
         </is>
       </c>
-      <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="B22" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=c8debce1")</f>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Betta Koi Vàng</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Thân vàng cam đốm xanh, đuôi vàng chuyển trắng xanh · màu gốc theo mô hình</t>
         </is>
       </c>
-      <c r="E21" s="4">
+      <c r="E22" s="4">
         <v>1400</v>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Solid</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1.5</t>
         </is>
@@ -3261,7 +3294,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=43252278")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -3302,15 +3335,15 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueBeeBetta</t>
+          <t xml:space="preserve">BlueFlameBetta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9950f4a4")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Ong Xanh</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3347,15 +3380,15 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueFlameBetta</t>
+          <t xml:space="preserve">BluePandaBetta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=1cbc3e15")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3392,15 +3425,15 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BluePandaBetta</t>
+          <t xml:space="preserve">BlueWildBetta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=e36e243b")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -3437,15 +3470,15 @@
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueWildBetta</t>
+          <t xml:space="preserve">ColorfulBetta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=5cc1541c")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Rồng Xanh</t>
+          <t xml:space="preserve">Colorful Betta</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3482,15 +3515,15 @@
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ColorfulBetta</t>
+          <t xml:space="preserve">EmeraldRedBetta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/emerald-red-betta.png?v=c2d27f6b")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colorful Betta</t>
+          <t xml:space="preserve">Betta Lục Bảo Đỏ</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3531,7 +3564,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=ab617dcf")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -3576,7 +3609,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b85cc880")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -3621,7 +3654,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=798a58a8")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -3666,7 +3699,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=f57fa2a7")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -3703,7 +3736,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=0a139958")</f>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -3748,7 +3781,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d3f82500")</f>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -3785,11 +3818,11 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=a66df8df")</f>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
+          <t xml:space="preserve">Koi Galaxy Betta</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3818,15 +3851,15 @@
     <row r="17" ht="66" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PurpleRubyBetta</t>
+          <t xml:space="preserve">PurpleMoonBetta</t>
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-moon-betta.png?v=f988dcb3")</f>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+          <t xml:space="preserve">Betta Trăng Tím</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3863,15 +3896,15 @@
     <row r="18" ht="66" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedSteelBetta</t>
+          <t xml:space="preserve">PurpleRubyBetta</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=8b2a77a6")</f>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3908,15 +3941,15 @@
     <row r="19" ht="66" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RoyalKoiBetta</t>
+          <t xml:space="preserve">RedSteelBetta</t>
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=e29f7895")</f>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Red Steel Betta</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -3953,15 +3986,15 @@
     <row r="20" ht="66" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">RoyalKoiBetta</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=413784be")</f>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -3998,15 +4031,15 @@
     <row r="21" ht="66" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBettaM4</t>
+          <t xml:space="preserve">SkyKoiBetta</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=974c7f77")</f>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta M4</t>
+          <t xml:space="preserve">Sky Koi Betta</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -4043,15 +4076,15 @@
     <row r="22" ht="66" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TealWhiteBetta</t>
+          <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=099e8b9d")</f>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+          <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4088,43 +4121,88 @@
     <row r="23" ht="66" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TealWhiteBetta</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=a25361f1")</f>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeshyColour</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">YellowKoiBetta</t>
         </is>
       </c>
-      <c r="B23" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B24" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=c8debce1")</f>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Betta Koi Vàng</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MeshyColour</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4296,7 +4374,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=43252278")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -4337,15 +4415,15 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueBeeBetta</t>
+          <t xml:space="preserve">BlueFlameBetta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9950f4a4")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Ong Xanh</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4382,15 +4460,15 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueFlameBetta</t>
+          <t xml:space="preserve">BluePandaBetta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=1cbc3e15")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4427,15 +4505,15 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BluePandaBetta</t>
+          <t xml:space="preserve">BlueWildBetta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=e36e243b")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4472,15 +4550,15 @@
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueWildBetta</t>
+          <t xml:space="preserve">ColorfulBetta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=5cc1541c")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Rồng Xanh</t>
+          <t xml:space="preserve">Colorful Betta</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -4517,15 +4595,15 @@
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ColorfulBetta</t>
+          <t xml:space="preserve">EmeraldRedBetta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/emerald-red-betta.png?v=c2d27f6b")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colorful Betta</t>
+          <t xml:space="preserve">Betta Lục Bảo Đỏ</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -4566,7 +4644,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=ab617dcf")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -4611,7 +4689,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b85cc880")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -4656,7 +4734,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=798a58a8")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -4701,7 +4779,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=f57fa2a7")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -4746,7 +4824,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=0a139958")</f>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -4791,7 +4869,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d3f82500")</f>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -4836,11 +4914,11 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=a66df8df")</f>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
+          <t xml:space="preserve">Koi Galaxy Betta</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -4877,15 +4955,15 @@
     <row r="17" ht="66" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PurpleRubyBetta</t>
+          <t xml:space="preserve">PurpleMoonBetta</t>
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-moon-betta.png?v=f988dcb3")</f>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+          <t xml:space="preserve">Betta Trăng Tím</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -4922,15 +5000,15 @@
     <row r="18" ht="66" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedSteelBetta</t>
+          <t xml:space="preserve">PurpleRubyBetta</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=8b2a77a6")</f>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -4967,15 +5045,15 @@
     <row r="19" ht="66" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RoyalKoiBetta</t>
+          <t xml:space="preserve">RedSteelBetta</t>
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=e29f7895")</f>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Red Steel Betta</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -5012,15 +5090,15 @@
     <row r="20" ht="66" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">RoyalKoiBetta</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=413784be")</f>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -5057,15 +5135,15 @@
     <row r="21" ht="66" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBettaM4</t>
+          <t xml:space="preserve">SkyKoiBetta</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=974c7f77")</f>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta M4</t>
+          <t xml:space="preserve">Sky Koi Betta</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -5102,15 +5180,15 @@
     <row r="22" ht="66" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TealWhiteBetta</t>
+          <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=099e8b9d")</f>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+          <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -5147,43 +5225,88 @@
     <row r="23" ht="66" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TealWhiteBetta</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=a25361f1")</f>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">YellowKoiBetta</t>
         </is>
       </c>
-      <c r="B23" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B24" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=c8debce1")</f>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Betta Koi Vàng</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5213,6 +5336,7 @@
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5263,40 +5387,45 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">headPatch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">pigmentDepth</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">scaleRelief</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">scaleEdge</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">scaleEdgeWidth</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">vibrance</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">brightness</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">envReflection</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">baseTexture</t>
         </is>
@@ -5340,16 +5469,16 @@
         <v>0</v>
       </c>
       <c r="K2" s="3">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
         <v>1</v>
       </c>
-      <c r="L2" s="3">
+      <c r="M2" s="3">
         <v>0</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>0.5</v>
-      </c>
-      <c r="N2" s="3">
-        <v>1</v>
       </c>
       <c r="O2" s="3">
         <v>1</v>
@@ -5358,6 +5487,9 @@
         <v>1</v>
       </c>
       <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5395,28 +5527,33 @@
       <c r="I3" s="4">
         <v>0</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" s="4">
         <v>0</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>0.55</v>
       </c>
-      <c r="L3" s="4">
+      <c r="M3" s="4">
         <v>0</v>
       </c>
-      <c r="M3" s="4">
+      <c r="N3" s="4">
         <v>0.35</v>
       </c>
-      <c r="N3" s="4">
+      <c r="O3" s="4">
         <v>1.3</v>
       </c>
-      <c r="O3" s="4">
+      <c r="P3" s="4">
         <v>1.2</v>
       </c>
-      <c r="P3" s="4">
+      <c r="Q3" s="4">
         <v>0</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="R3" s="4">
         <v>1</v>
       </c>
     </row>
@@ -5427,7 +5564,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=43252278")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -5500,6 +5637,11 @@
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5508,15 +5650,15 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueBeeBetta</t>
+          <t xml:space="preserve">BlueFlameBetta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9950f4a4")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Ong Xanh</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -5585,6 +5727,11 @@
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5593,15 +5740,15 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueFlameBetta</t>
+          <t xml:space="preserve">BluePandaBetta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=1cbc3e15")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -5670,6 +5817,11 @@
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5678,15 +5830,15 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BluePandaBetta</t>
+          <t xml:space="preserve">BlueWildBetta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=e36e243b")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -5755,6 +5907,11 @@
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5763,15 +5920,15 @@
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueWildBetta</t>
+          <t xml:space="preserve">ColorfulBetta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=5cc1541c")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Rồng Xanh</t>
+          <t xml:space="preserve">Colorful Betta</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -5840,6 +5997,11 @@
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5848,21 +6010,19 @@
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ColorfulBetta</t>
+          <t xml:space="preserve">EmeraldRedBetta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/emerald-red-betta.png?v=c2d27f6b")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colorful Betta</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">Betta Lục Bảo Đỏ</t>
+        </is>
+      </c>
+      <c r="D9" s="4">
+        <v>0.25</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -5874,10 +6034,8 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="G9" s="4">
+        <v>1.4</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -5914,17 +6072,18 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="O9" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1.35</v>
       </c>
       <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5937,7 +6096,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=ab617dcf")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -6010,6 +6169,11 @@
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6022,7 +6186,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b85cc880")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -6095,6 +6259,11 @@
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6107,7 +6276,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=798a58a8")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -6182,6 +6351,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="13" ht="66" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -6190,7 +6364,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=f57fa2a7")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -6215,17 +6389,17 @@
       <c r="I13" s="4">
         <v>0</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" s="4">
         <v>0</v>
       </c>
-      <c r="K13" s="4">
+      <c r="L13" s="4">
         <v>0.55</v>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6247,6 +6421,11 @@
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6259,7 +6438,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=0a139958")</f>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -6332,6 +6511,11 @@
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6344,7 +6528,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d3f82500")</f>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -6369,17 +6553,17 @@
       <c r="I15" s="4">
         <v>0</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K15" s="4">
         <v>0</v>
       </c>
-      <c r="K15" s="4">
+      <c r="L15" s="4">
         <v>0.55</v>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -6401,6 +6585,11 @@
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6413,11 +6602,11 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=a66df8df")</f>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
+          <t xml:space="preserve">Koi Galaxy Betta</t>
         </is>
       </c>
       <c r="D16" s="4">
@@ -6439,29 +6628,32 @@
         <v>0.04</v>
       </c>
       <c r="J16" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K16" s="4">
         <v>0.35</v>
       </c>
-      <c r="K16" s="4">
-        <v>0</v>
-      </c>
       <c r="L16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M16" s="4">
         <v>1</v>
       </c>
-      <c r="M16" s="4">
+      <c r="N16" s="4">
         <v>0.35</v>
       </c>
-      <c r="N16" s="4">
+      <c r="O16" s="4">
         <v>1.3</v>
       </c>
-      <c r="O16" s="4">
+      <c r="P16" s="4">
         <v>1.12</v>
       </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6470,21 +6662,19 @@
     <row r="17" ht="66" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PurpleRubyBetta</t>
+          <t xml:space="preserve">PurpleMoonBetta</t>
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-moon-betta.png?v=f988dcb3")</f>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">Betta Trăng Tím</t>
+        </is>
+      </c>
+      <c r="D17" s="4">
+        <v>0.5</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -6496,10 +6686,8 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="G17" s="4">
+        <v>1.2</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -6546,7 +6734,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="Q17" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6555,15 +6746,15 @@
     <row r="18" ht="66" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedSteelBetta</t>
+          <t xml:space="preserve">PurpleRubyBetta</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=8b2a77a6")</f>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -6632,6 +6823,11 @@
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6640,15 +6836,15 @@
     <row r="19" ht="66" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RoyalKoiBetta</t>
+          <t xml:space="preserve">RedSteelBetta</t>
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=e29f7895")</f>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Red Steel Betta</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -6717,6 +6913,11 @@
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6725,15 +6926,15 @@
     <row r="20" ht="66" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">RoyalKoiBetta</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=413784be")</f>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -6802,6 +7003,11 @@
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6810,15 +7016,15 @@
     <row r="21" ht="66" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBettaM4</t>
+          <t xml:space="preserve">SkyKoiBetta</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=974c7f77")</f>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta M4</t>
+          <t xml:space="preserve">Sky Koi Betta</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -6887,6 +7093,11 @@
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6895,15 +7106,15 @@
     <row r="22" ht="66" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TealWhiteBetta</t>
+          <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=099e8b9d")</f>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+          <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -6972,6 +7183,11 @@
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6980,83 +7196,178 @@
     <row r="23" ht="66" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TealWhiteBetta</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=a25361f1")</f>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">YellowKoiBetta</t>
         </is>
       </c>
-      <c r="B23" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B24" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=c8debce1")</f>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Betta Koi Vàng</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7248,7 +7559,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=1a297ceb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/black-samurai-betta.png?v=43252278")</f>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -7304,15 +7615,15 @@
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueBeeBetta</t>
+          <t xml:space="preserve">BlueFlameBetta</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-bee-betta.png?v=f43bfe73")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=9950f4a4")</f>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Ong Xanh</t>
+          <t xml:space="preserve">Blue Flame Betta</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -7364,15 +7675,15 @@
     <row r="6" ht="66" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueFlameBetta</t>
+          <t xml:space="preserve">BluePandaBetta</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-flame-betta.png?v=cdd432e5")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=1cbc3e15")</f>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blue Flame Betta</t>
+          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -7424,15 +7735,15 @@
     <row r="7" ht="66" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BluePandaBetta</t>
+          <t xml:space="preserve">BlueWildBetta</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-panda-betta.png?v=36b3bf65")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=e36e243b")</f>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Gấu Trúc Xanh</t>
+          <t xml:space="preserve">Betta Rồng Xanh</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -7484,15 +7795,15 @@
     <row r="8" ht="66" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BlueWildBetta</t>
+          <t xml:space="preserve">ColorfulBetta</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/blue-wild-betta.png?v=680bdef4")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=5cc1541c")</f>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Rồng Xanh</t>
+          <t xml:space="preserve">Colorful Betta</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -7544,15 +7855,15 @@
     <row r="9" ht="66" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ColorfulBetta</t>
+          <t xml:space="preserve">EmeraldRedBetta</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/colorful-betta.png?v=b244d109")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/emerald-red-betta.png?v=c2d27f6b")</f>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colorful Betta</t>
+          <t xml:space="preserve">Betta Lục Bảo Đỏ</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -7608,7 +7919,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=c0b59211")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/galaxy-betta.png?v=ab617dcf")</f>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -7668,7 +7979,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b4f93beb")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/gold-tiger-betta.png?v=b85cc880")</f>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -7728,7 +8039,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=e769ef5b")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-betta.png?v=798a58a8")</f>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -7788,7 +8099,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=e1ab2904")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/koi-nemo.png?v=f57fa2a7")</f>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -7838,7 +8149,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=8fa1bfac")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/nemo-koi-betta.png?v=0a139958")</f>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -7898,7 +8209,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=217c12a3")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat.png?v=d3f82500")</f>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -7948,11 +8259,11 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=82c21339")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/plakat-galaxy.png?v=a66df8df")</f>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plakat Galaxy</t>
+          <t xml:space="preserve">Koi Galaxy Betta</t>
         </is>
       </c>
       <c r="D16" s="4">
@@ -7990,15 +8301,15 @@
     <row r="17" ht="66" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PurpleRubyBetta</t>
+          <t xml:space="preserve">PurpleMoonBetta</t>
         </is>
       </c>
       <c r="B17" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=dd6ba697")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-moon-betta.png?v=f988dcb3")</f>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
+          <t xml:space="preserve">Betta Trăng Tím</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -8050,15 +8361,15 @@
     <row r="18" ht="66" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedSteelBetta</t>
+          <t xml:space="preserve">PurpleRubyBetta</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=b64f1149")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/purple-ruby-betta.png?v=8b2a77a6")</f>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Steel Betta</t>
+          <t xml:space="preserve">Betta Hồng Ngọc Tím</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -8110,15 +8421,15 @@
     <row r="19" ht="66" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RoyalKoiBetta</t>
+          <t xml:space="preserve">RedSteelBetta</t>
         </is>
       </c>
       <c r="B19" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=e1d369c0")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/red-steel-betta.png?v=e29f7895")</f>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royal Koi</t>
+          <t xml:space="preserve">Red Steel Betta</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -8170,15 +8481,15 @@
     <row r="20" ht="66" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBetta</t>
+          <t xml:space="preserve">RoyalKoiBetta</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=b28bfda2")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/royal-koi-betta.png?v=413784be")</f>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta</t>
+          <t xml:space="preserve">Royal Koi</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -8230,15 +8541,15 @@
     <row r="21" ht="66" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SkyKoiBettaM4</t>
+          <t xml:space="preserve">SkyKoiBetta</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=17abc1d1")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta.png?v=974c7f77")</f>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky Koi Betta M4</t>
+          <t xml:space="preserve">Sky Koi Betta</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -8290,15 +8601,15 @@
     <row r="22" ht="66" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TealWhiteBetta</t>
+          <t xml:space="preserve">SkyKoiBettaM4</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=de86fbc9")</f>
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/sky-koi-betta-m4.png?v=099e8b9d")</f>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+          <t xml:space="preserve">Sky Koi Betta M4</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -8350,58 +8661,118 @@
     <row r="23" ht="66" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TealWhiteBetta</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/teal-white-betta.png?v=a25361f1")</f>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betta Trắng Ngọc Lam</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">YellowKoiBetta</t>
         </is>
       </c>
-      <c r="B23" s="3">
-        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=0adb4476")</f>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B24" s="3">
+        <f>IMAGE("https://pub-590970a58ce5426989b3bcd2897271b4.r2.dev/sheet-images/fish/yellow-koi-betta.png?v=c8debce1")</f>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Betta Koi Vàng</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
